--- a/Test.xlsx
+++ b/Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prac608\Desktop\P_I_Sym_KW2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2371BDCD-44D1-4525-9779-0609186A0188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95061A83-A30B-44A2-842A-620726FBFF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{77F83A4A-FCFB-4AD2-8380-C974F3AD45E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{77F83A4A-FCFB-4AD2-8380-C974F3AD45E5}"/>
   </bookViews>
   <sheets>
     <sheet name="sekcja 1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Arkusz3" sheetId="3" r:id="rId3"/>
     <sheet name="sekcja3" sheetId="4" r:id="rId4"/>
     <sheet name="Arkusz5" sheetId="5" r:id="rId5"/>
+    <sheet name="sekcja4" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
   <si>
     <t>Dane z lat 2010 - 2023 dotyczące wartości sprzedaży w tys. zł:</t>
   </si>
@@ -583,7 +584,129 @@
     <t>1.</t>
   </si>
   <si>
+    <t>9.</t>
+  </si>
+  <si>
     <t>Górna granica prognozy przedziałowej Y dla X1=65 oraz X2=15 w okresie prognozy wyniesie:</t>
+  </si>
+  <si>
+    <t>Marginalny/krańcowy przyrost zmiennej zależnej w modelu względem zmiennej objaśniającej X1 w modelu wyniesie:</t>
+  </si>
+  <si>
+    <t>Przyrost jednostkowy zmiennej Y względem zmiennej X2 w modelu wyniesie:</t>
+  </si>
+  <si>
+    <t>Wartość oczekiwana składnika losowego w modelu wyniesie:</t>
+  </si>
+  <si>
+    <r>
+      <t>Prognoza punktowa Y (dla wartości zmiennych objaśniających w okresie prognozy: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>X1=65 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>oraz </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>X2=15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>) wyniesie:</t>
+    </r>
+  </si>
+  <si>
+    <t>Błąd bezwzględny prognozy punktowej Y dla X1=65 oraz X2=15 w okresie prognozy wyniesie:</t>
+  </si>
+  <si>
+    <t>Błąd względny prognozy punktowej Y dla X1=65 oraz X2=15 w okresie prognozy wyniesie (wynik wpisz w formacie procentowym, samą liczbę - bez znaku%)</t>
+  </si>
+  <si>
+    <t>Dolna granica prognozy przedziałowej Y dla X1=65 oraz X2=15 w okresie prognozy wyniesie:</t>
+  </si>
+  <si>
+    <t>10.</t>
+  </si>
+  <si>
+    <t>Określ czy prognoza punktowa Y dla X1=65 oraz X2=15 jest dopuszczalna czy nie (wpisz słowo TAK lub słowo NIE):</t>
+  </si>
+  <si>
+    <t>Tak 7,85&lt;10</t>
+  </si>
+  <si>
+    <t>Dana jest tabela zawierająca wartości kształtowania się zmiennej Y w latach 2010-2023</t>
+  </si>
+  <si>
+    <t>Prognoza punktowa Y dla roku 2024 wykonana metodą wyrównywania wykładniczego Browna ze stała wygładzania alfa =0,22 wyniesie (dla roku 2010 jako prognozy użyj wartości empirycznej z tego roku): </t>
+  </si>
+  <si>
+    <t>Wartość prognozy Y dla roku 2024 wykonanej metodą wyrównywania wykładniczego Browna dla stałej wygładzania alfa=0,44 (jako prognozy dla roku 2010 użyj wartości średniej z całego szeregu) wyniesie:</t>
+  </si>
+  <si>
+    <t>Określ wartość stałej wygładzania alfa dla której prognoza Y daje najmniejszy z możliwych wartości pierwiastka ze średniego kwadratowego błędu ex post (Sp/RMSE) (prognoza Y w 2010=wartość empiryczna Y z 2010) - wartość stałej wygładzania podaj do 4 miejsc po przecinku</t>
+  </si>
+  <si>
+    <t>Wartość pierwiastka ze średniego kwadratowego błędu ex post (Sp/RMSE) dla stałej wygładzania alfa=0,44 (dla roku 2010 jako prognozy użyj średniej z wartości empirycznych Y z całego szeregu) wyniesie:</t>
+  </si>
+  <si>
+    <t>Wartość względnego błędu prognozy ex post dla stałej wygładzania alfa=0,22 (jako prognozy dla roku 2010 użyj wartości empirycznej Y z tegoż roku) wyniesie - wartość błędu podaj w formacie procentowym - samą liczbę - bez znaku%</t>
+  </si>
+  <si>
+    <t>Podaj wartość prognozy Y dla  roku 2020, dla stałej wygładzania 0,22 (przy założeniu, że prognoza dla 1 okresu równa się wartości empirycznej z tego okresu) :</t>
+  </si>
+  <si>
+    <t>Określ który z modeli adaptacyjnych znajduje zastosowanie w prognozowaniu szeregów charakteryzujących się trendem oraz wahaniami sezonowymi i losowymi</t>
+  </si>
+  <si>
+    <t>Pytanie 30Wybierz jedną odpowiedź:</t>
+  </si>
+  <si>
+    <t>A.</t>
+  </si>
+  <si>
+    <t>Wintersa</t>
+  </si>
+  <si>
+    <t>B.</t>
+  </si>
+  <si>
+    <t>Browna</t>
+  </si>
+  <si>
+    <t>C.</t>
+  </si>
+  <si>
+    <t>Holta</t>
   </si>
 </sst>
 </file>
@@ -698,6 +821,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D118-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D118-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D118-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -937,6 +1072,161 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>228600</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>60960</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6145" name="Control 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s6145"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24223D68-F4A1-41B4-80F7-5E2BD2AA73BB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>228600</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>60960</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6146" name="Control 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s6146"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7EBE0D4-A73A-49BA-8CF7-176D678BFCBD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>228600</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>60960</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6147" name="Control 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s6147"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32727783-81F1-477E-A877-D687808D2668}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -2334,7 +2624,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5020A19-C32B-4B86-8830-63547366D4F5}">
-  <dimension ref="B13:J29"/>
+  <dimension ref="B13:J36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="13" spans="2:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -2376,7 +2666,7 @@
         <v>426.13</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>220</v>
       </c>
@@ -2387,7 +2677,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>250</v>
       </c>
@@ -2401,10 +2691,10 @@
         <v>14</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>290</v>
       </c>
@@ -2414,8 +2704,11 @@
       <c r="D19" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <v>744.92</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>330</v>
       </c>
@@ -2425,8 +2718,14 @@
       <c r="D20" s="1">
         <v>74</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>350</v>
       </c>
@@ -2437,7 +2736,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>430</v>
       </c>
@@ -2447,8 +2746,14 @@
       <c r="D22" s="1">
         <v>72</v>
       </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>420</v>
       </c>
@@ -2459,7 +2764,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>440</v>
       </c>
@@ -2469,8 +2774,14 @@
       <c r="D24" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="1">
         <v>485</v>
       </c>
@@ -2481,7 +2792,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="1">
         <v>500</v>
       </c>
@@ -2491,8 +2802,14 @@
       <c r="D26" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="1">
         <v>550</v>
       </c>
@@ -2502,13 +2819,56 @@
       <c r="D27" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <v>632.59</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="10"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="10" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F34" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="G36" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2669,4 +3029,301 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07906ADE-4B02-472B-9C5D-58BBBB8A28DF}">
+  <sheetPr codeName="Arkusz1"/>
+  <dimension ref="B2:P30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2010</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2011</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2012</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2013</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2014</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2015</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2016</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2017</v>
+      </c>
+      <c r="K3" s="1">
+        <v>2018</v>
+      </c>
+      <c r="L3" s="1">
+        <v>2019</v>
+      </c>
+      <c r="M3" s="1">
+        <v>2020</v>
+      </c>
+      <c r="N3" s="1">
+        <v>2021</v>
+      </c>
+      <c r="O3" s="1">
+        <v>2022</v>
+      </c>
+      <c r="P3" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1">
+        <v>99</v>
+      </c>
+      <c r="D4" s="1">
+        <v>111</v>
+      </c>
+      <c r="E4" s="1">
+        <v>105</v>
+      </c>
+      <c r="F4" s="1">
+        <v>105</v>
+      </c>
+      <c r="G4" s="1">
+        <v>111</v>
+      </c>
+      <c r="H4" s="1">
+        <v>99</v>
+      </c>
+      <c r="I4" s="1">
+        <v>111</v>
+      </c>
+      <c r="J4" s="1">
+        <v>99</v>
+      </c>
+      <c r="K4" s="1">
+        <v>105</v>
+      </c>
+      <c r="L4" s="1">
+        <v>111</v>
+      </c>
+      <c r="M4" s="1">
+        <v>117</v>
+      </c>
+      <c r="N4" s="1">
+        <v>108</v>
+      </c>
+      <c r="O4" s="1">
+        <v>111</v>
+      </c>
+      <c r="P4" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="228" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6147" r:id="rId3" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>60960</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6147" r:id="rId3" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6146" r:id="rId5" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>60960</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6146" r:id="rId5" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6145" r:id="rId6" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>22</xdr:row>
+                <xdr:rowOff>60960</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6145" r:id="rId6" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
 </file>